--- a/results/excel_reports/independent_vgg16_gray.xlsx
+++ b/results/excel_reports/independent_vgg16_gray.xlsx
@@ -401,6 +401,38 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Top-1 Accuracy'!A9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Top-1 Accuracy'!$B$9:$V$9</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -722,6 +754,38 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Top-5 Accuracy'!A9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$9:$V$9</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -795,7 +859,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -822,7 +886,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1132,11 +1196,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -1232,68 +1296,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dino448</t>
+          <t>dino+u2net_sum</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8168168168168168</v>
       </c>
       <c r="C2" t="n">
-        <v>0.792</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.765</v>
+        <v>0.793</v>
       </c>
       <c r="E2" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.742</v>
       </c>
-      <c r="F2" t="n">
-        <v>0.707</v>
-      </c>
       <c r="G2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.713</v>
       </c>
       <c r="H2" t="n">
-        <v>0.662</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.638</v>
+        <v>0.677</v>
       </c>
       <c r="J2" t="n">
-        <v>0.614</v>
+        <v>0.651</v>
       </c>
       <c r="K2" t="n">
-        <v>0.583</v>
+        <v>0.619</v>
       </c>
       <c r="L2" t="n">
-        <v>0.554</v>
+        <v>0.588</v>
       </c>
       <c r="M2" t="n">
-        <v>0.514</v>
+        <v>0.546</v>
       </c>
       <c r="N2" t="n">
-        <v>0.485</v>
+        <v>0.481</v>
       </c>
       <c r="O2" t="n">
-        <v>0.453</v>
+        <v>0.433</v>
       </c>
       <c r="P2" t="n">
-        <v>0.382</v>
+        <v>0.374</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.338</v>
+        <v>0.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0.287</v>
+        <v>0.24</v>
       </c>
       <c r="S2" t="n">
-        <v>0.218</v>
+        <v>0.168</v>
       </c>
       <c r="T2" t="n">
-        <v>0.136</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.063</v>
+        <v>0.029</v>
       </c>
       <c r="V2" t="n">
         <v>0.001</v>
@@ -1302,68 +1366,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>u2net+dino_320</t>
+          <t>dino</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8168168168168168</v>
       </c>
       <c r="C3" t="n">
-        <v>0.79</v>
+        <v>0.805</v>
       </c>
       <c r="D3" t="n">
-        <v>0.748</v>
+        <v>0.803</v>
       </c>
       <c r="E3" t="n">
-        <v>0.737</v>
+        <v>0.785</v>
       </c>
       <c r="F3" t="n">
-        <v>0.708</v>
+        <v>0.766</v>
       </c>
       <c r="G3" t="n">
-        <v>0.672</v>
+        <v>0.739</v>
       </c>
       <c r="H3" t="n">
-        <v>0.658</v>
+        <v>0.716</v>
       </c>
       <c r="I3" t="n">
-        <v>0.643</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.623</v>
+        <v>0.677</v>
       </c>
       <c r="K3" t="n">
-        <v>0.607</v>
+        <v>0.65</v>
       </c>
       <c r="L3" t="n">
-        <v>0.57</v>
+        <v>0.626</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.603</v>
       </c>
       <c r="N3" t="n">
-        <v>0.514</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.48</v>
+        <v>0.503</v>
       </c>
       <c r="P3" t="n">
-        <v>0.433</v>
+        <v>0.446</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.381</v>
+        <v>0.387</v>
       </c>
       <c r="R3" t="n">
         <v>0.333</v>
       </c>
       <c r="S3" t="n">
-        <v>0.259</v>
+        <v>0.265</v>
       </c>
       <c r="T3" t="n">
-        <v>0.162</v>
+        <v>0.171</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="V3" t="n">
         <v>0.001</v>
@@ -1372,68 +1436,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dino+u2net_sum</t>
+          <t>dino448</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8168168168168168</v>
       </c>
       <c r="C4" t="n">
-        <v>0.791</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.75</v>
+        <v>0.801</v>
       </c>
       <c r="E4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.735</v>
       </c>
-      <c r="F4" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.669</v>
-      </c>
       <c r="H4" t="n">
-        <v>0.659</v>
+        <v>0.712</v>
       </c>
       <c r="I4" t="n">
-        <v>0.641</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.633</v>
+        <v>0.677</v>
       </c>
       <c r="K4" t="n">
-        <v>0.603</v>
+        <v>0.654</v>
       </c>
       <c r="L4" t="n">
-        <v>0.581</v>
+        <v>0.611</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.597</v>
       </c>
       <c r="N4" t="n">
-        <v>0.519</v>
+        <v>0.548</v>
       </c>
       <c r="O4" t="n">
-        <v>0.491</v>
+        <v>0.489</v>
       </c>
       <c r="P4" t="n">
-        <v>0.451</v>
+        <v>0.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.382</v>
+        <v>0.391</v>
       </c>
       <c r="R4" t="n">
-        <v>0.293</v>
+        <v>0.33</v>
       </c>
       <c r="S4" t="n">
-        <v>0.192</v>
+        <v>0.256</v>
       </c>
       <c r="T4" t="n">
-        <v>0.093</v>
+        <v>0.169</v>
       </c>
       <c r="U4" t="n">
-        <v>0.033</v>
+        <v>0.082</v>
       </c>
       <c r="V4" t="n">
         <v>0.001</v>
@@ -1442,68 +1506,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>u2net+dino</t>
+          <t>u2net+dino_320</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8168168168168168</v>
       </c>
       <c r="C5" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="D5" t="n">
         <v>0.791</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.75</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.735</v>
+        <v>0.769</v>
       </c>
       <c r="F5" t="n">
-        <v>0.715</v>
+        <v>0.749</v>
       </c>
       <c r="G5" t="n">
-        <v>0.669</v>
+        <v>0.714</v>
       </c>
       <c r="H5" t="n">
-        <v>0.659</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.638</v>
+        <v>0.677</v>
       </c>
       <c r="J5" t="n">
-        <v>0.631</v>
+        <v>0.66</v>
       </c>
       <c r="K5" t="n">
-        <v>0.605</v>
+        <v>0.632</v>
       </c>
       <c r="L5" t="n">
-        <v>0.574</v>
+        <v>0.611</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.595</v>
       </c>
       <c r="N5" t="n">
-        <v>0.513</v>
+        <v>0.544</v>
       </c>
       <c r="O5" t="n">
-        <v>0.483</v>
+        <v>0.509</v>
       </c>
       <c r="P5" t="n">
-        <v>0.437</v>
+        <v>0.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.383</v>
+        <v>0.405</v>
       </c>
       <c r="R5" t="n">
-        <v>0.334</v>
+        <v>0.368</v>
       </c>
       <c r="S5" t="n">
-        <v>0.262</v>
+        <v>0.275</v>
       </c>
       <c r="T5" t="n">
-        <v>0.165</v>
+        <v>0.188</v>
       </c>
       <c r="U5" t="n">
-        <v>0.073</v>
+        <v>0.094</v>
       </c>
       <c r="V5" t="n">
         <v>0.001</v>
@@ -1512,68 +1576,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>u2net</t>
+          <t>u2net+dino</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8168168168168168</v>
       </c>
       <c r="C6" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="D6" t="n">
         <v>0.793</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.781</v>
-      </c>
       <c r="E6" t="n">
-        <v>0.766</v>
+        <v>0.769</v>
       </c>
       <c r="F6" t="n">
-        <v>0.744</v>
+        <v>0.742</v>
       </c>
       <c r="G6" t="n">
-        <v>0.725</v>
+        <v>0.716</v>
       </c>
       <c r="H6" t="n">
-        <v>0.701</v>
+        <v>0.697</v>
       </c>
       <c r="I6" t="n">
-        <v>0.676</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.667</v>
+        <v>0.665</v>
       </c>
       <c r="K6" t="n">
-        <v>0.644</v>
+        <v>0.638</v>
       </c>
       <c r="L6" t="n">
-        <v>0.629</v>
+        <v>0.612</v>
       </c>
       <c r="M6" t="n">
-        <v>0.601</v>
+        <v>0.595</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.544</v>
       </c>
       <c r="O6" t="n">
-        <v>0.509</v>
+        <v>0.513</v>
       </c>
       <c r="P6" t="n">
-        <v>0.469</v>
+        <v>0.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.407</v>
+        <v>0.414</v>
       </c>
       <c r="R6" t="n">
-        <v>0.347</v>
+        <v>0.373</v>
       </c>
       <c r="S6" t="n">
-        <v>0.259</v>
+        <v>0.275</v>
       </c>
       <c r="T6" t="n">
-        <v>0.16</v>
+        <v>0.191</v>
       </c>
       <c r="U6" t="n">
-        <v>0.062</v>
+        <v>0.097</v>
       </c>
       <c r="V6" t="n">
         <v>0.001</v>
@@ -1582,68 +1646,68 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dino448+u2net</t>
+          <t>u2net</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8168168168168168</v>
       </c>
       <c r="C7" t="n">
-        <v>0.798</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.764</v>
+        <v>0.804</v>
       </c>
       <c r="E7" t="n">
-        <v>0.746</v>
+        <v>0.774</v>
       </c>
       <c r="F7" t="n">
-        <v>0.724</v>
+        <v>0.753</v>
       </c>
       <c r="G7" t="n">
-        <v>0.701</v>
+        <v>0.73</v>
       </c>
       <c r="H7" t="n">
-        <v>0.677</v>
+        <v>0.72</v>
       </c>
       <c r="I7" t="n">
-        <v>0.657</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.654</v>
+        <v>0.662</v>
       </c>
       <c r="K7" t="n">
-        <v>0.655</v>
+        <v>0.648</v>
       </c>
       <c r="L7" t="n">
-        <v>0.623</v>
+        <v>0.63</v>
       </c>
       <c r="M7" t="n">
-        <v>0.588</v>
+        <v>0.621</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.571</v>
       </c>
       <c r="O7" t="n">
-        <v>0.52</v>
+        <v>0.546</v>
       </c>
       <c r="P7" t="n">
-        <v>0.473</v>
+        <v>0.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.409</v>
+        <v>0.43</v>
       </c>
       <c r="R7" t="n">
-        <v>0.362</v>
+        <v>0.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0.301</v>
+        <v>0.291</v>
       </c>
       <c r="T7" t="n">
-        <v>0.195</v>
+        <v>0.167</v>
       </c>
       <c r="U7" t="n">
-        <v>0.101</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>0.001</v>
@@ -1652,75 +1716,145 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>dino448+u2net</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8168168168168168</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>dinov2_COMBO_ENT_SMOOTH</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
+        <v>0.8168168168168168</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.8179999999999999</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.704</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="D9" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.658</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.446</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="L9" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="V9" t="n">
         <v>0.001</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:V8">
+  <conditionalFormatting sqref="B2:V9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1743,11 +1877,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -1843,68 +1977,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dino448</t>
+          <t>dino+u2net_sum</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0.9569569569569569</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.952</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.9379999999999999</v>
-      </c>
       <c r="D2" t="n">
-        <v>0.925</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.908</v>
+        <v>0.927</v>
       </c>
       <c r="F2" t="n">
-        <v>0.898</v>
+        <v>0.912</v>
       </c>
       <c r="G2" t="n">
-        <v>0.877</v>
+        <v>0.9</v>
       </c>
       <c r="H2" t="n">
-        <v>0.854</v>
+        <v>0.875</v>
       </c>
       <c r="I2" t="n">
-        <v>0.844</v>
+        <v>0.849</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.837</v>
       </c>
       <c r="K2" t="n">
-        <v>0.791</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>0.781</v>
+        <v>0.788</v>
       </c>
       <c r="M2" t="n">
-        <v>0.743</v>
+        <v>0.751</v>
       </c>
       <c r="N2" t="n">
-        <v>0.714</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.671</v>
+        <v>0.636</v>
       </c>
       <c r="P2" t="n">
-        <v>0.62</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.549</v>
+        <v>0.48</v>
       </c>
       <c r="R2" t="n">
-        <v>0.472</v>
+        <v>0.394</v>
       </c>
       <c r="S2" t="n">
-        <v>0.383</v>
+        <v>0.287</v>
       </c>
       <c r="T2" t="n">
-        <v>0.273</v>
+        <v>0.174</v>
       </c>
       <c r="U2" t="n">
-        <v>0.136</v>
+        <v>0.063</v>
       </c>
       <c r="V2" t="n">
         <v>0.005</v>
@@ -1913,68 +2047,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dino+u2net_sum</t>
+          <t>dino448</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.952</v>
+        <v>0.9569569569569569</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.951</v>
       </c>
       <c r="D3" t="n">
-        <v>0.914</v>
+        <v>0.949</v>
       </c>
       <c r="E3" t="n">
-        <v>0.901</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.894</v>
+        <v>0.927</v>
       </c>
       <c r="G3" t="n">
-        <v>0.869</v>
+        <v>0.91</v>
       </c>
       <c r="H3" t="n">
-        <v>0.859</v>
+        <v>0.895</v>
       </c>
       <c r="I3" t="n">
-        <v>0.836</v>
+        <v>0.881</v>
       </c>
       <c r="J3" t="n">
-        <v>0.823</v>
+        <v>0.858</v>
       </c>
       <c r="K3" t="n">
-        <v>0.795</v>
+        <v>0.848</v>
       </c>
       <c r="L3" t="n">
-        <v>0.783</v>
+        <v>0.82</v>
       </c>
       <c r="M3" t="n">
-        <v>0.761</v>
+        <v>0.801</v>
       </c>
       <c r="N3" t="n">
-        <v>0.747</v>
+        <v>0.768</v>
       </c>
       <c r="O3" t="n">
-        <v>0.696</v>
+        <v>0.725</v>
       </c>
       <c r="P3" t="n">
-        <v>0.662</v>
+        <v>0.678</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.585</v>
+        <v>0.605</v>
       </c>
       <c r="R3" t="n">
-        <v>0.489</v>
+        <v>0.537</v>
       </c>
       <c r="S3" t="n">
-        <v>0.333</v>
+        <v>0.452</v>
       </c>
       <c r="T3" t="n">
-        <v>0.178</v>
+        <v>0.319</v>
       </c>
       <c r="U3" t="n">
-        <v>0.068</v>
+        <v>0.171</v>
       </c>
       <c r="V3" t="n">
         <v>0.005</v>
@@ -1983,68 +2117,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>u2net+dino</t>
+          <t>dino</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.952</v>
+        <v>0.9569569569569569</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="D4" t="n">
-        <v>0.914</v>
+        <v>0.946</v>
       </c>
       <c r="E4" t="n">
-        <v>0.901</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.894</v>
+        <v>0.925</v>
       </c>
       <c r="G4" t="n">
-        <v>0.868</v>
+        <v>0.91</v>
       </c>
       <c r="H4" t="n">
-        <v>0.858</v>
+        <v>0.896</v>
       </c>
       <c r="I4" t="n">
-        <v>0.834</v>
+        <v>0.88</v>
       </c>
       <c r="J4" t="n">
-        <v>0.823</v>
+        <v>0.864</v>
       </c>
       <c r="K4" t="n">
-        <v>0.795</v>
+        <v>0.85</v>
       </c>
       <c r="L4" t="n">
-        <v>0.784</v>
+        <v>0.825</v>
       </c>
       <c r="M4" t="n">
-        <v>0.759</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.745</v>
+        <v>0.777</v>
       </c>
       <c r="O4" t="n">
-        <v>0.703</v>
+        <v>0.727</v>
       </c>
       <c r="P4" t="n">
-        <v>0.655</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.597</v>
+        <v>0.617</v>
       </c>
       <c r="R4" t="n">
-        <v>0.53</v>
+        <v>0.551</v>
       </c>
       <c r="S4" t="n">
-        <v>0.443</v>
+        <v>0.454</v>
       </c>
       <c r="T4" t="n">
-        <v>0.31</v>
+        <v>0.325</v>
       </c>
       <c r="U4" t="n">
-        <v>0.153</v>
+        <v>0.173</v>
       </c>
       <c r="V4" t="n">
         <v>0.005</v>
@@ -2053,68 +2187,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>u2net+dino_320</t>
+          <t>u2net+dino</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>0.9569569569569569</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.952</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.9350000000000001</v>
-      </c>
       <c r="D5" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.912</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.891</v>
-      </c>
       <c r="G5" t="n">
-        <v>0.867</v>
+        <v>0.901</v>
       </c>
       <c r="H5" t="n">
-        <v>0.858</v>
+        <v>0.879</v>
       </c>
       <c r="I5" t="n">
-        <v>0.834</v>
+        <v>0.856</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.848</v>
       </c>
       <c r="K5" t="n">
-        <v>0.795</v>
+        <v>0.832</v>
       </c>
       <c r="L5" t="n">
-        <v>0.783</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.762</v>
+        <v>0.799</v>
       </c>
       <c r="N5" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="O5" t="n">
         <v>0.74</v>
       </c>
-      <c r="O5" t="n">
-        <v>0.7</v>
-      </c>
       <c r="P5" t="n">
-        <v>0.659</v>
+        <v>0.694</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.599</v>
+        <v>0.624</v>
       </c>
       <c r="R5" t="n">
-        <v>0.529</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>0.445</v>
+        <v>0.479</v>
       </c>
       <c r="T5" t="n">
-        <v>0.313</v>
+        <v>0.338</v>
       </c>
       <c r="U5" t="n">
-        <v>0.151</v>
+        <v>0.184</v>
       </c>
       <c r="V5" t="n">
         <v>0.005</v>
@@ -2123,68 +2257,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>u2net</t>
+          <t>u2net+dino_320</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.952</v>
+        <v>0.9569569569569569</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.953</v>
       </c>
       <c r="D6" t="n">
-        <v>0.93</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.917</v>
+        <v>0.928</v>
       </c>
       <c r="F6" t="n">
-        <v>0.902</v>
+        <v>0.916</v>
       </c>
       <c r="G6" t="n">
-        <v>0.896</v>
+        <v>0.899</v>
       </c>
       <c r="H6" t="n">
-        <v>0.895</v>
+        <v>0.879</v>
       </c>
       <c r="I6" t="n">
-        <v>0.878</v>
+        <v>0.858</v>
       </c>
       <c r="J6" t="n">
-        <v>0.863</v>
+        <v>0.845</v>
       </c>
       <c r="K6" t="n">
-        <v>0.838</v>
+        <v>0.831</v>
       </c>
       <c r="L6" t="n">
-        <v>0.822</v>
+        <v>0.82</v>
       </c>
       <c r="M6" t="n">
-        <v>0.797</v>
+        <v>0.794</v>
       </c>
       <c r="N6" t="n">
         <v>0.764</v>
       </c>
       <c r="O6" t="n">
-        <v>0.736</v>
+        <v>0.74</v>
       </c>
       <c r="P6" t="n">
-        <v>0.701</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.625</v>
+        <v>0.628</v>
       </c>
       <c r="R6" t="n">
-        <v>0.54</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>0.433</v>
+        <v>0.479</v>
       </c>
       <c r="T6" t="n">
-        <v>0.284</v>
+        <v>0.35</v>
       </c>
       <c r="U6" t="n">
-        <v>0.147</v>
+        <v>0.176</v>
       </c>
       <c r="V6" t="n">
         <v>0.005</v>
@@ -2193,68 +2327,68 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dino448+u2net</t>
+          <t>u2net</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.952</v>
+        <v>0.9569569569569569</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.954</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.951</v>
       </c>
       <c r="E7" t="n">
-        <v>0.91</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.899</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.887</v>
+        <v>0.914</v>
       </c>
       <c r="H7" t="n">
-        <v>0.877</v>
+        <v>0.898</v>
       </c>
       <c r="I7" t="n">
-        <v>0.862</v>
+        <v>0.893</v>
       </c>
       <c r="J7" t="n">
-        <v>0.844</v>
+        <v>0.868</v>
       </c>
       <c r="K7" t="n">
-        <v>0.835</v>
+        <v>0.857</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="M7" t="n">
-        <v>0.796</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.78</v>
+        <v>0.785</v>
       </c>
       <c r="O7" t="n">
-        <v>0.737</v>
+        <v>0.763</v>
       </c>
       <c r="P7" t="n">
-        <v>0.696</v>
+        <v>0.704</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.644</v>
+        <v>0.649</v>
       </c>
       <c r="R7" t="n">
-        <v>0.576</v>
+        <v>0.569</v>
       </c>
       <c r="S7" t="n">
-        <v>0.491</v>
+        <v>0.458</v>
       </c>
       <c r="T7" t="n">
-        <v>0.368</v>
+        <v>0.322</v>
       </c>
       <c r="U7" t="n">
-        <v>0.195</v>
+        <v>0.155</v>
       </c>
       <c r="V7" t="n">
         <v>0.005</v>
@@ -2267,71 +2401,141 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.952</v>
+        <v>0.9569569569569569</v>
       </c>
       <c r="C8" t="n">
-        <v>0.946</v>
+        <v>0.956</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="E8" t="n">
-        <v>0.928</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.921</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.909</v>
+        <v>0.925</v>
       </c>
       <c r="H8" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.897</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.877</v>
-      </c>
       <c r="K8" t="n">
-        <v>0.856</v>
+        <v>0.869</v>
       </c>
       <c r="L8" t="n">
-        <v>0.834</v>
+        <v>0.854</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.838</v>
       </c>
       <c r="N8" t="n">
-        <v>0.785</v>
+        <v>0.805</v>
       </c>
       <c r="O8" t="n">
-        <v>0.759</v>
+        <v>0.771</v>
       </c>
       <c r="P8" t="n">
-        <v>0.714</v>
+        <v>0.739</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.658</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>0.57</v>
+        <v>0.606</v>
       </c>
       <c r="S8" t="n">
-        <v>0.489</v>
+        <v>0.517</v>
       </c>
       <c r="T8" t="n">
-        <v>0.365</v>
+        <v>0.402</v>
       </c>
       <c r="U8" t="n">
-        <v>0.213</v>
+        <v>0.236</v>
       </c>
       <c r="V8" t="n">
         <v>0.005</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dino448+u2net</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9569569569569569</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:V8">
+  <conditionalFormatting sqref="B2:V9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
